--- a/5/search/FY2_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY2_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,37 +492,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>296.2</v>
+        <v>295.4</v>
       </c>
       <c r="B2" t="n">
-        <v>118.1</v>
+        <v>116.6</v>
       </c>
       <c r="C2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>12427.56309796058</v>
+        <v>12400.11069243845</v>
       </c>
       <c r="F2" t="n">
-        <v>531.0770496399869</v>
+        <v>557.3688388171129</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12677.84393579117</v>
+        <v>12650.17987521249</v>
       </c>
       <c r="I2" t="n">
-        <v>22.43922503900347</v>
+        <v>30.72436307780845</v>
       </c>
       <c r="J2" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.900000000000002</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="L2" t="n">
         <v>14</v>
@@ -530,113 +530,113 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>297.8</v>
+        <v>262.6</v>
       </c>
       <c r="B3" t="n">
-        <v>119.1</v>
+        <v>137</v>
       </c>
       <c r="C3" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="E3" t="n">
-        <v>12455.48252068874</v>
+        <v>11940.00701111417</v>
       </c>
       <c r="F3" t="n">
-        <v>536.1005279854447</v>
+        <v>938.0795725619564</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>12722.10643523825</v>
+        <v>11825.31453236185</v>
       </c>
       <c r="I3" t="n">
-        <v>30.40327607448546</v>
+        <v>54.99640245981425</v>
       </c>
       <c r="J3" t="n">
-        <v>1287.104</v>
+        <v>1192.975</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>258.6</v>
+        <v>276.4</v>
       </c>
       <c r="B4" t="n">
-        <v>137.5</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>11907.59519337276</v>
+        <v>12084.13675002933</v>
       </c>
       <c r="F4" t="n">
-        <v>941.723225864345</v>
+        <v>649.9039746175818</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>11728.2211569787</v>
+        <v>12152.3557365396</v>
       </c>
       <c r="I4" t="n">
-        <v>52.12713489513226</v>
+        <v>41.71800809129672</v>
       </c>
       <c r="J4" t="n">
-        <v>1186.556</v>
+        <v>1223.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>297.8</v>
+        <v>292.2</v>
       </c>
       <c r="B5" t="n">
-        <v>116.1</v>
+        <v>119.6</v>
       </c>
       <c r="C5" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>12465.66840491377</v>
+        <v>12334.40420996582</v>
       </c>
       <c r="F5" t="n">
-        <v>516.7812794867473</v>
+        <v>580.5674976197621</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12725.57635184238</v>
+        <v>12560.35300048326</v>
       </c>
       <c r="I5" t="n">
-        <v>23.82199361888536</v>
+        <v>26.89688790338516</v>
       </c>
       <c r="J5" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.899999999999999</v>
+        <v>3.900000000000002</v>
       </c>
       <c r="L5" t="n">
         <v>14</v>
@@ -644,227 +644,227 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>299.4</v>
+        <v>269</v>
       </c>
       <c r="B6" t="n">
-        <v>117.1</v>
+        <v>136.5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>12494.36953411566</v>
+        <v>11990.47098608524</v>
       </c>
       <c r="F6" t="n">
-        <v>522.6354193733021</v>
+        <v>854.0831584446104</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>12770.29671594766</v>
+        <v>11976.17746521311</v>
       </c>
       <c r="I6" t="n">
-        <v>32.94356041886607</v>
+        <v>35.20789611152588</v>
       </c>
       <c r="J6" t="n">
-        <v>1287.104</v>
+        <v>1223.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.899999999999999</v>
+        <v>3.900000000000002</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>243.8</v>
+        <v>301.8</v>
       </c>
       <c r="B7" t="n">
-        <v>106.1</v>
+        <v>113.6</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="E7" t="n">
-        <v>11672.09360313157</v>
+        <v>12586.64934801054</v>
       </c>
       <c r="F7" t="n">
-        <v>733.6062088428763</v>
+        <v>453.8314627515841</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>11334.8184520669</v>
+        <v>12856.02915066844</v>
       </c>
       <c r="I7" t="n">
-        <v>48.17259508126347</v>
+        <v>19.36631809669927</v>
       </c>
       <c r="J7" t="n">
-        <v>1145.984</v>
+        <v>1300.775</v>
       </c>
       <c r="K7" t="n">
-        <v>3.800000000000002</v>
+        <v>3.900000000000002</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>293</v>
+        <v>274.8</v>
       </c>
       <c r="B8" t="n">
-        <v>117.1</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>12338.5841520811</v>
+        <v>12067.64516854984</v>
       </c>
       <c r="F8" t="n">
-        <v>602.3457242893222</v>
+        <v>594.4351725827007</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>12576.50815084078</v>
+        <v>12114.83947218927</v>
       </c>
       <c r="I8" t="n">
-        <v>41.83190892506207</v>
+        <v>32.41319996598031</v>
       </c>
       <c r="J8" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.800000000000001</v>
+        <v>3.900000000000002</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>294.6</v>
+        <v>274.8</v>
       </c>
       <c r="B9" t="n">
-        <v>117.1</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>12399.72114234428</v>
+        <v>12063.16003614723</v>
       </c>
       <c r="F9" t="n">
-        <v>526.9333033708242</v>
+        <v>647.847189838474</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>12633.70425005801</v>
+        <v>12114.37087626661</v>
       </c>
       <c r="I9" t="n">
-        <v>15.86987119764802</v>
+        <v>37.99355997777741</v>
       </c>
       <c r="J9" t="n">
-        <v>1287.104</v>
+        <v>1223.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.800000000000001</v>
+        <v>3.900000000000002</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>269.2</v>
+        <v>259.4</v>
       </c>
       <c r="B10" t="n">
-        <v>97.5</v>
+        <v>139</v>
       </c>
       <c r="C10" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E10" t="n">
-        <v>11989.38176185208</v>
+        <v>11913.06459170043</v>
       </c>
       <c r="F10" t="n">
-        <v>639.5741304909242</v>
+        <v>935.4647539919206</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11980.94162383707</v>
+        <v>11746.86454642184</v>
       </c>
       <c r="I10" t="n">
-        <v>35.13305472729974</v>
+        <v>47.38266603529837</v>
       </c>
       <c r="J10" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K10" t="n">
-        <v>3.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>267.6</v>
+        <v>276.4</v>
       </c>
       <c r="B11" t="n">
-        <v>100.5</v>
+        <v>94</v>
       </c>
       <c r="C11" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="D11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>11968.85707632159</v>
+        <v>12090.11148479559</v>
       </c>
       <c r="F11" t="n">
-        <v>656.952351255479</v>
+        <v>596.6380141505739</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>11942.76435648293</v>
+        <v>12152.97996255996</v>
       </c>
       <c r="I11" t="n">
-        <v>34.39891582088023</v>
+        <v>36.1529077439975</v>
       </c>
       <c r="J11" t="n">
-        <v>1211.644</v>
+        <v>1223.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>9</v>

--- a/5/search/FY2_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY2_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,382 +492,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>295.4</v>
+        <v>285.6</v>
       </c>
       <c r="B2" t="n">
-        <v>116.6</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="E2" t="n">
-        <v>12400.11069243845</v>
+        <v>12210.83313936237</v>
       </c>
       <c r="F2" t="n">
-        <v>557.3688388171129</v>
+        <v>644.8805476306361</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12650.17987521249</v>
+        <v>12379.49965085226</v>
       </c>
       <c r="I2" t="n">
-        <v>30.72436307780845</v>
+        <v>40.78498573514503</v>
       </c>
       <c r="J2" t="n">
-        <v>1277.5</v>
+        <v>1246.336</v>
       </c>
       <c r="K2" t="n">
         <v>4.000000000000002</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>262.6</v>
+        <v>289.6</v>
       </c>
       <c r="B3" t="n">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="E3" t="n">
-        <v>11940.00701111417</v>
+        <v>12280.50460262516</v>
       </c>
       <c r="F3" t="n">
-        <v>938.0795725619564</v>
+        <v>612.2515579792627</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>11825.31453236185</v>
+        <v>12485.19715048677</v>
       </c>
       <c r="I3" t="n">
-        <v>54.99640245981425</v>
+        <v>37.40810028845431</v>
       </c>
       <c r="J3" t="n">
-        <v>1192.975</v>
+        <v>1257.116</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>276.4</v>
+        <v>293.8</v>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>12084.13675002933</v>
+        <v>12364.9663660211</v>
       </c>
       <c r="F4" t="n">
-        <v>649.9039746175818</v>
+        <v>572.5104763966185</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>12152.3557365396</v>
+        <v>12605.07581735077</v>
       </c>
       <c r="I4" t="n">
-        <v>41.71800809129672</v>
+        <v>28.10947402597276</v>
       </c>
       <c r="J4" t="n">
-        <v>1223.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>292.2</v>
+        <v>293</v>
       </c>
       <c r="B5" t="n">
-        <v>119.6</v>
+        <v>117.6</v>
       </c>
       <c r="C5" t="n">
         <v>7.4</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="E5" t="n">
-        <v>12334.40420996582</v>
+        <v>12340.02985725651</v>
       </c>
       <c r="F5" t="n">
-        <v>580.5674976197621</v>
+        <v>598.9398563315482</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12560.35300048326</v>
+        <v>12578.96975695027</v>
       </c>
       <c r="I5" t="n">
-        <v>26.89688790338516</v>
+        <v>36.03272834831171</v>
       </c>
       <c r="J5" t="n">
-        <v>1277.5</v>
+        <v>1267.504</v>
       </c>
       <c r="K5" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>269</v>
+        <v>300.2</v>
       </c>
       <c r="B6" t="n">
-        <v>136.5</v>
+        <v>118</v>
       </c>
       <c r="C6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12510.46464184036</v>
+      </c>
+      <c r="F6" t="n">
+        <v>522.9339309773804</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12795.37513961173</v>
+      </c>
+      <c r="I6" t="n">
+        <v>33.40868315080218</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1287.104</v>
+      </c>
+      <c r="K6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11990.47098608524</v>
-      </c>
-      <c r="F6" t="n">
-        <v>854.0831584446104</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="H6" t="n">
-        <v>11976.17746521311</v>
-      </c>
-      <c r="I6" t="n">
-        <v>35.20789611152588</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1223.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.900000000000002</v>
-      </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>301.8</v>
+        <v>275.3</v>
       </c>
       <c r="B7" t="n">
-        <v>113.6</v>
+        <v>135.4</v>
       </c>
       <c r="C7" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>12586.64934801054</v>
+        <v>12050.02791016106</v>
       </c>
       <c r="F7" t="n">
-        <v>453.8314627515841</v>
+        <v>860.7155034632303</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>12856.02915066844</v>
+        <v>12125.06977540264</v>
       </c>
       <c r="I7" t="n">
-        <v>19.36631809669927</v>
+        <v>51.78875865807584</v>
       </c>
       <c r="J7" t="n">
-        <v>1300.775</v>
+        <v>1223.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>274.8</v>
+        <v>284.8</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>111.6</v>
       </c>
       <c r="C8" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="E8" t="n">
-        <v>12067.64516854984</v>
+        <v>12199.55422609944</v>
       </c>
       <c r="F8" t="n">
-        <v>594.4351725827007</v>
+        <v>644.7175688221963</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>12114.83947218927</v>
+        <v>12359.19760697899</v>
       </c>
       <c r="I8" t="n">
-        <v>32.41319996598031</v>
+        <v>40.49162387995341</v>
       </c>
       <c r="J8" t="n">
-        <v>1223.6</v>
+        <v>1246.336</v>
       </c>
       <c r="K8" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>274.8</v>
+        <v>274.5</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>135.6</v>
       </c>
       <c r="C9" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>12063.16003614723</v>
+        <v>12042.55621352278</v>
       </c>
       <c r="F9" t="n">
-        <v>647.847189838474</v>
+        <v>859.2720381831514</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>12114.37087626661</v>
+        <v>12106.39053380696</v>
       </c>
       <c r="I9" t="n">
-        <v>37.99355997777741</v>
+        <v>48.18009545787845</v>
       </c>
       <c r="J9" t="n">
         <v>1223.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>259.4</v>
+        <v>277.7</v>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>136.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D10" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="E10" t="n">
-        <v>11913.06459170043</v>
+        <v>12076.98310269393</v>
       </c>
       <c r="F10" t="n">
-        <v>935.4647539919206</v>
+        <v>830.6206927718436</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11746.86454642184</v>
+        <v>12183.29310165222</v>
       </c>
       <c r="I10" t="n">
-        <v>47.38266603529837</v>
+        <v>44.33498279010371</v>
       </c>
       <c r="J10" t="n">
-        <v>1192.975</v>
+        <v>1235.164</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>276.4</v>
+        <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>94</v>
+        <v>117.8</v>
       </c>
       <c r="C11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>12090.11148479559</v>
+        <v>12427.84064695455</v>
       </c>
       <c r="F11" t="n">
-        <v>596.6380141505739</v>
+        <v>560.315451604882</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>12152.97996255996</v>
+        <v>12695.24105130114</v>
       </c>
       <c r="I11" t="n">
-        <v>36.1529077439975</v>
+        <v>35.51260885793329</v>
       </c>
       <c r="J11" t="n">
-        <v>1223.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
